--- a/storage/app/assessTemplate/renovation.xlsx
+++ b/storage/app/assessTemplate/renovation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\excel\評価シートテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA44C765-12F1-48AE-A4A9-6F7F21671A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5AD080-10EF-4522-B43A-36EFCF992494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3AD99582-2449-4C94-B98B-43D8E1CCF0F2}"/>
   </bookViews>
@@ -453,12 +453,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="#,##0&quot;円&quot;"/>
     <numFmt numFmtId="177" formatCode="0&quot;年&quot;"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
     <numFmt numFmtId="179" formatCode="0.0000%"/>
     <numFmt numFmtId="180" formatCode="0.00000000_ "/>
+    <numFmt numFmtId="182" formatCode="General\%"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1012,7 +1013,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1112,10 +1113,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1147,10 +1144,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1287,6 +1280,17 @@
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1645,8 +1649,8 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
       <c r="R1" s="3" t="s">
         <v>49</v>
       </c>
@@ -1917,7 +1921,7 @@
       <c r="Q8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="32"/>
+      <c r="R8" s="85"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -1939,11 +1943,11 @@
       <c r="E9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34" t="s">
+      <c r="F9" s="32"/>
+      <c r="G9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="84"/>
       <c r="I9" s="2" t="s">
         <v>13</v>
       </c>
@@ -1953,17 +1957,17 @@
       <c r="K9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N9" s="37"/>
-      <c r="O9" s="38"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="37"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="39"/>
+      <c r="R9" s="38"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
@@ -1983,9 +1987,9 @@
       <c r="C10" s="23"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1997,7 +2001,7 @@
       <c r="Q10" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="43"/>
+      <c r="R10" s="86"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -2013,24 +2017,24 @@
       <c r="AE10" s="4"/>
     </row>
     <row r="11" spans="2:31" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="48"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="46"/>
       <c r="P11" s="2"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
@@ -2080,7 +2084,7 @@
       <c r="Q12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="R12" s="49"/>
+      <c r="R12" s="47"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
@@ -2113,17 +2117,17 @@
       <c r="K13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L13" s="50"/>
+      <c r="L13" s="48"/>
       <c r="M13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N13" s="25"/>
       <c r="O13" s="26"/>
       <c r="P13" s="2"/>
-      <c r="Q13" s="78" t="s">
+      <c r="Q13" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="R13" s="81"/>
+      <c r="R13" s="79"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -2154,8 +2158,8 @@
       <c r="N14" s="2"/>
       <c r="O14" s="31"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="79"/>
-      <c r="R14" s="82"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="80"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -2199,15 +2203,15 @@
       <c r="K15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="84" t="s">
+      <c r="L15" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
+      <c r="M15" s="82"/>
+      <c r="N15" s="82"/>
       <c r="O15" s="31"/>
       <c r="P15" s="2"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="83"/>
+      <c r="Q15" s="78"/>
+      <c r="R15" s="81"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -2229,11 +2233,11 @@
       <c r="E16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="33"/>
+      <c r="F16" s="32"/>
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="84"/>
       <c r="I16" s="2" t="s">
         <v>13</v>
       </c>
@@ -2243,17 +2247,17 @@
       <c r="K16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L16" s="36"/>
+      <c r="L16" s="35"/>
       <c r="M16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N16" s="37"/>
-      <c r="O16" s="38"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="37"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="R16" s="51"/>
+      <c r="R16" s="49"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -2269,20 +2273,20 @@
       <c r="AE16" s="4"/>
     </row>
     <row r="17" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="56"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="54"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="4"/>
@@ -2301,7 +2305,7 @@
       <c r="AE17" s="4"/>
     </row>
     <row r="18" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="55" t="s">
         <v>34</v>
       </c>
       <c r="C18" s="16" t="s">
@@ -2310,7 +2314,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="47"/>
+      <c r="G18" s="45"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2342,7 +2346,7 @@
       <c r="E19" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="56" t="s">
         <v>36</v>
       </c>
       <c r="G19" s="17" t="s">
@@ -2354,7 +2358,7 @@
       <c r="I19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="J19" s="58" t="s">
+      <c r="J19" s="56" t="s">
         <v>39</v>
       </c>
       <c r="K19" s="2"/>
@@ -2385,15 +2389,15 @@
       <c r="E20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="35"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="37"/>
+      <c r="J20" s="36"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2417,20 +2421,20 @@
       <c r="AE20" s="4"/>
     </row>
     <row r="21" spans="1:31" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="52"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="56"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="54"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="4"/>
@@ -2449,7 +2453,7 @@
       <c r="AE21" s="4"/>
     </row>
     <row r="22" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="55" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="16" t="s">
@@ -2466,7 +2470,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="48"/>
+      <c r="O22" s="46"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="4"/>
@@ -2499,7 +2503,7 @@
       <c r="G23" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="59">
+      <c r="H23" s="57">
         <v>1</v>
       </c>
       <c r="I23" s="17" t="s">
@@ -2517,7 +2521,7 @@
       <c r="M23" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="N23" s="60" t="s">
+      <c r="N23" s="58" t="s">
         <v>46</v>
       </c>
       <c r="O23" s="20"/>
@@ -2557,15 +2561,15 @@
       <c r="I24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="35"/>
+      <c r="J24" s="34"/>
       <c r="K24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L24" s="35"/>
+      <c r="L24" s="34"/>
       <c r="M24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N24" s="61"/>
+      <c r="N24" s="59"/>
       <c r="O24" s="20"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
@@ -2593,13 +2597,13 @@
       <c r="G25" s="2"/>
       <c r="H25" s="30"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="62"/>
+      <c r="J25" s="60"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="85" t="s">
+      <c r="L25" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="M25" s="85"/>
-      <c r="N25" s="61"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="59"/>
       <c r="O25" s="20"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
@@ -2619,20 +2623,20 @@
       <c r="AE25" s="4"/>
     </row>
     <row r="26" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="63"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="66"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="64"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="4"/>
@@ -2652,22 +2656,22 @@
     </row>
     <row r="27" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="72"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="70"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -2685,20 +2689,20 @@
     </row>
     <row r="28" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
-      <c r="K28" s="73"/>
-      <c r="L28" s="73"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="73"/>
-      <c r="O28" s="74"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="72"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -2716,20 +2720,20 @@
     </row>
     <row r="29" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="73"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="73"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="74"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="72"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -2747,20 +2751,20 @@
     </row>
     <row r="30" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="75"/>
-      <c r="D30" s="75"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="75"/>
-      <c r="M30" s="75"/>
-      <c r="N30" s="75"/>
-      <c r="O30" s="76"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="74"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
@@ -2777,7 +2781,7 @@
       <c r="AE30" s="1"/>
     </row>
     <row r="31" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="67"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="4"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -3260,1204 +3264,1204 @@
       <c r="AE46" s="4"/>
     </row>
     <row r="47" spans="3:31" x14ac:dyDescent="0.4">
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="67"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="67"/>
-      <c r="M47" s="67"/>
-      <c r="N47" s="67"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="65"/>
+      <c r="Q47" s="65"/>
     </row>
     <row r="48" spans="3:31" x14ac:dyDescent="0.4">
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="67"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="67"/>
-      <c r="K48" s="67"/>
-      <c r="L48" s="67"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="67"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="67"/>
-      <c r="Q48" s="67"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="65"/>
+      <c r="L48" s="65"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="65"/>
+      <c r="P48" s="65"/>
+      <c r="Q48" s="65"/>
     </row>
     <row r="49" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="67"/>
-      <c r="K49" s="67"/>
-      <c r="L49" s="67"/>
-      <c r="M49" s="67"/>
-      <c r="N49" s="67"/>
-      <c r="O49" s="67"/>
-      <c r="P49" s="67"/>
-      <c r="Q49" s="67"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="65"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="65"/>
+      <c r="H49" s="65"/>
+      <c r="I49" s="65"/>
+      <c r="J49" s="65"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="65"/>
+      <c r="P49" s="65"/>
+      <c r="Q49" s="65"/>
     </row>
     <row r="50" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D50" s="67"/>
-      <c r="E50" s="67"/>
-      <c r="F50" s="67"/>
-      <c r="G50" s="67"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="67"/>
-      <c r="J50" s="67"/>
-      <c r="K50" s="67"/>
-      <c r="L50" s="67"/>
-      <c r="M50" s="67"/>
-      <c r="N50" s="67"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="67"/>
-      <c r="Q50" s="67"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="65"/>
+      <c r="I50" s="65"/>
+      <c r="J50" s="65"/>
+      <c r="K50" s="65"/>
+      <c r="L50" s="65"/>
+      <c r="M50" s="65"/>
+      <c r="N50" s="65"/>
+      <c r="O50" s="65"/>
+      <c r="P50" s="65"/>
+      <c r="Q50" s="65"/>
     </row>
     <row r="51" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
-      <c r="F51" s="67"/>
-      <c r="G51" s="67"/>
-      <c r="H51" s="67"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="67"/>
-      <c r="K51" s="67"/>
-      <c r="L51" s="67"/>
-      <c r="M51" s="67"/>
-      <c r="N51" s="67"/>
-      <c r="O51" s="67"/>
-      <c r="P51" s="67"/>
-      <c r="Q51" s="67"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="65"/>
+      <c r="K51" s="65"/>
+      <c r="L51" s="65"/>
+      <c r="M51" s="65"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="65"/>
+      <c r="Q51" s="65"/>
     </row>
     <row r="52" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
-      <c r="H52" s="67"/>
-      <c r="I52" s="67"/>
-      <c r="J52" s="67"/>
-      <c r="K52" s="67"/>
-      <c r="L52" s="67"/>
-      <c r="M52" s="67"/>
-      <c r="N52" s="67"/>
-      <c r="O52" s="67"/>
-      <c r="P52" s="67"/>
-      <c r="Q52" s="67"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="65"/>
+      <c r="I52" s="65"/>
+      <c r="J52" s="65"/>
+      <c r="K52" s="65"/>
+      <c r="L52" s="65"/>
+      <c r="M52" s="65"/>
+      <c r="N52" s="65"/>
+      <c r="O52" s="65"/>
+      <c r="P52" s="65"/>
+      <c r="Q52" s="65"/>
     </row>
     <row r="53" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
-      <c r="H53" s="67"/>
-      <c r="I53" s="67"/>
-      <c r="J53" s="67"/>
-      <c r="K53" s="67"/>
-      <c r="L53" s="67"/>
-      <c r="M53" s="67"/>
-      <c r="N53" s="67"/>
-      <c r="O53" s="67"/>
-      <c r="P53" s="67"/>
-      <c r="Q53" s="67"/>
+      <c r="D53" s="65"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="65"/>
+      <c r="H53" s="65"/>
+      <c r="I53" s="65"/>
+      <c r="J53" s="65"/>
+      <c r="K53" s="65"/>
+      <c r="L53" s="65"/>
+      <c r="M53" s="65"/>
+      <c r="N53" s="65"/>
+      <c r="O53" s="65"/>
+      <c r="P53" s="65"/>
+      <c r="Q53" s="65"/>
     </row>
     <row r="54" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="67"/>
-      <c r="G54" s="67"/>
-      <c r="H54" s="67"/>
-      <c r="I54" s="67"/>
-      <c r="J54" s="67"/>
-      <c r="K54" s="67"/>
-      <c r="L54" s="67"/>
-      <c r="M54" s="67"/>
-      <c r="N54" s="67"/>
-      <c r="O54" s="67"/>
-      <c r="P54" s="67"/>
-      <c r="Q54" s="67"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="65"/>
+      <c r="I54" s="65"/>
+      <c r="J54" s="65"/>
+      <c r="K54" s="65"/>
+      <c r="L54" s="65"/>
+      <c r="M54" s="65"/>
+      <c r="N54" s="65"/>
+      <c r="O54" s="65"/>
+      <c r="P54" s="65"/>
+      <c r="Q54" s="65"/>
     </row>
     <row r="55" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="67"/>
-      <c r="J55" s="67"/>
-      <c r="K55" s="67"/>
-      <c r="L55" s="67"/>
-      <c r="M55" s="67"/>
-      <c r="N55" s="67"/>
-      <c r="O55" s="67"/>
-      <c r="P55" s="67"/>
-      <c r="Q55" s="67"/>
+      <c r="D55" s="65"/>
+      <c r="E55" s="65"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="65"/>
+      <c r="J55" s="65"/>
+      <c r="K55" s="65"/>
+      <c r="L55" s="65"/>
+      <c r="M55" s="65"/>
+      <c r="N55" s="65"/>
+      <c r="O55" s="65"/>
+      <c r="P55" s="65"/>
+      <c r="Q55" s="65"/>
     </row>
     <row r="56" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D56" s="67"/>
-      <c r="E56" s="67"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="67"/>
-      <c r="I56" s="67"/>
-      <c r="J56" s="67"/>
-      <c r="K56" s="67"/>
-      <c r="L56" s="67"/>
-      <c r="M56" s="67"/>
-      <c r="N56" s="67"/>
-      <c r="O56" s="67"/>
-      <c r="P56" s="67"/>
-      <c r="Q56" s="67"/>
+      <c r="D56" s="65"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="65"/>
+      <c r="H56" s="65"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
+      <c r="K56" s="65"/>
+      <c r="L56" s="65"/>
+      <c r="M56" s="65"/>
+      <c r="N56" s="65"/>
+      <c r="O56" s="65"/>
+      <c r="P56" s="65"/>
+      <c r="Q56" s="65"/>
     </row>
     <row r="57" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="67"/>
-      <c r="I57" s="67"/>
-      <c r="J57" s="67"/>
-      <c r="K57" s="67"/>
-      <c r="L57" s="67"/>
-      <c r="M57" s="67"/>
-      <c r="N57" s="67"/>
-      <c r="O57" s="67"/>
-      <c r="P57" s="67"/>
-      <c r="Q57" s="67"/>
+      <c r="D57" s="65"/>
+      <c r="E57" s="65"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="65"/>
+      <c r="J57" s="65"/>
+      <c r="K57" s="65"/>
+      <c r="L57" s="65"/>
+      <c r="M57" s="65"/>
+      <c r="N57" s="65"/>
+      <c r="O57" s="65"/>
+      <c r="P57" s="65"/>
+      <c r="Q57" s="65"/>
     </row>
     <row r="58" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D58" s="67"/>
-      <c r="E58" s="67"/>
-      <c r="F58" s="67"/>
-      <c r="G58" s="67"/>
-      <c r="H58" s="67"/>
-      <c r="I58" s="67"/>
-      <c r="J58" s="67"/>
-      <c r="K58" s="67"/>
-      <c r="L58" s="67"/>
-      <c r="M58" s="67"/>
-      <c r="N58" s="67"/>
-      <c r="O58" s="67"/>
-      <c r="P58" s="67"/>
-      <c r="Q58" s="67"/>
+      <c r="D58" s="65"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="65"/>
+      <c r="J58" s="65"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="65"/>
+      <c r="M58" s="65"/>
+      <c r="N58" s="65"/>
+      <c r="O58" s="65"/>
+      <c r="P58" s="65"/>
+      <c r="Q58" s="65"/>
     </row>
     <row r="59" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D59" s="67"/>
-      <c r="E59" s="67"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="67"/>
-      <c r="H59" s="67"/>
-      <c r="I59" s="67"/>
-      <c r="J59" s="67"/>
-      <c r="K59" s="67"/>
-      <c r="L59" s="67"/>
-      <c r="M59" s="67"/>
-      <c r="N59" s="67"/>
-      <c r="O59" s="67"/>
-      <c r="P59" s="67"/>
-      <c r="Q59" s="67"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65"/>
+      <c r="I59" s="65"/>
+      <c r="J59" s="65"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="65"/>
+      <c r="M59" s="65"/>
+      <c r="N59" s="65"/>
+      <c r="O59" s="65"/>
+      <c r="P59" s="65"/>
+      <c r="Q59" s="65"/>
     </row>
     <row r="60" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="67"/>
-      <c r="K60" s="67"/>
-      <c r="L60" s="67"/>
-      <c r="M60" s="67"/>
-      <c r="N60" s="67"/>
-      <c r="O60" s="67"/>
-      <c r="P60" s="67"/>
-      <c r="Q60" s="67"/>
+      <c r="D60" s="65"/>
+      <c r="E60" s="65"/>
+      <c r="F60" s="65"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="65"/>
+      <c r="I60" s="65"/>
+      <c r="J60" s="65"/>
+      <c r="K60" s="65"/>
+      <c r="L60" s="65"/>
+      <c r="M60" s="65"/>
+      <c r="N60" s="65"/>
+      <c r="O60" s="65"/>
+      <c r="P60" s="65"/>
+      <c r="Q60" s="65"/>
     </row>
     <row r="61" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="67"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="67"/>
-      <c r="L61" s="67"/>
-      <c r="M61" s="67"/>
-      <c r="N61" s="67"/>
-      <c r="O61" s="67"/>
-      <c r="P61" s="67"/>
-      <c r="Q61" s="67"/>
+      <c r="D61" s="65"/>
+      <c r="E61" s="65"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="65"/>
+      <c r="J61" s="65"/>
+      <c r="K61" s="65"/>
+      <c r="L61" s="65"/>
+      <c r="M61" s="65"/>
+      <c r="N61" s="65"/>
+      <c r="O61" s="65"/>
+      <c r="P61" s="65"/>
+      <c r="Q61" s="65"/>
     </row>
     <row r="62" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D62" s="67"/>
-      <c r="E62" s="67"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="67"/>
-      <c r="H62" s="67"/>
-      <c r="I62" s="67"/>
-      <c r="J62" s="67"/>
-      <c r="K62" s="67"/>
-      <c r="L62" s="67"/>
-      <c r="M62" s="67"/>
-      <c r="N62" s="67"/>
-      <c r="O62" s="67"/>
-      <c r="P62" s="67"/>
-      <c r="Q62" s="67"/>
+      <c r="D62" s="65"/>
+      <c r="E62" s="65"/>
+      <c r="F62" s="65"/>
+      <c r="G62" s="65"/>
+      <c r="H62" s="65"/>
+      <c r="I62" s="65"/>
+      <c r="J62" s="65"/>
+      <c r="K62" s="65"/>
+      <c r="L62" s="65"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="65"/>
+      <c r="O62" s="65"/>
+      <c r="P62" s="65"/>
+      <c r="Q62" s="65"/>
     </row>
     <row r="63" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D63" s="67"/>
-      <c r="E63" s="67"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="67"/>
-      <c r="H63" s="67"/>
-      <c r="I63" s="67"/>
-      <c r="J63" s="67"/>
-      <c r="K63" s="67"/>
-      <c r="L63" s="67"/>
-      <c r="M63" s="67"/>
-      <c r="N63" s="67"/>
-      <c r="O63" s="67"/>
-      <c r="P63" s="67"/>
-      <c r="Q63" s="67"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="65"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="65"/>
+      <c r="H63" s="65"/>
+      <c r="I63" s="65"/>
+      <c r="J63" s="65"/>
+      <c r="K63" s="65"/>
+      <c r="L63" s="65"/>
+      <c r="M63" s="65"/>
+      <c r="N63" s="65"/>
+      <c r="O63" s="65"/>
+      <c r="P63" s="65"/>
+      <c r="Q63" s="65"/>
     </row>
     <row r="64" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
-      <c r="H64" s="67"/>
-      <c r="I64" s="67"/>
-      <c r="J64" s="67"/>
-      <c r="K64" s="67"/>
-      <c r="L64" s="67"/>
-      <c r="M64" s="67"/>
-      <c r="N64" s="67"/>
-      <c r="O64" s="67"/>
-      <c r="P64" s="67"/>
-      <c r="Q64" s="67"/>
+      <c r="D64" s="65"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="65"/>
+      <c r="H64" s="65"/>
+      <c r="I64" s="65"/>
+      <c r="J64" s="65"/>
+      <c r="K64" s="65"/>
+      <c r="L64" s="65"/>
+      <c r="M64" s="65"/>
+      <c r="N64" s="65"/>
+      <c r="O64" s="65"/>
+      <c r="P64" s="65"/>
+      <c r="Q64" s="65"/>
     </row>
     <row r="65" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
-      <c r="H65" s="67"/>
-      <c r="I65" s="67"/>
-      <c r="J65" s="67"/>
-      <c r="K65" s="67"/>
-      <c r="L65" s="67"/>
-      <c r="M65" s="67"/>
-      <c r="N65" s="67"/>
-      <c r="O65" s="67"/>
-      <c r="P65" s="67"/>
-      <c r="Q65" s="67"/>
+      <c r="D65" s="65"/>
+      <c r="E65" s="65"/>
+      <c r="F65" s="65"/>
+      <c r="G65" s="65"/>
+      <c r="H65" s="65"/>
+      <c r="I65" s="65"/>
+      <c r="J65" s="65"/>
+      <c r="K65" s="65"/>
+      <c r="L65" s="65"/>
+      <c r="M65" s="65"/>
+      <c r="N65" s="65"/>
+      <c r="O65" s="65"/>
+      <c r="P65" s="65"/>
+      <c r="Q65" s="65"/>
     </row>
     <row r="66" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
-      <c r="H66" s="67"/>
-      <c r="I66" s="67"/>
-      <c r="J66" s="67"/>
-      <c r="K66" s="67"/>
-      <c r="L66" s="67"/>
-      <c r="M66" s="67"/>
-      <c r="N66" s="67"/>
-      <c r="O66" s="67"/>
-      <c r="P66" s="67"/>
-      <c r="Q66" s="67"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="65"/>
+      <c r="H66" s="65"/>
+      <c r="I66" s="65"/>
+      <c r="J66" s="65"/>
+      <c r="K66" s="65"/>
+      <c r="L66" s="65"/>
+      <c r="M66" s="65"/>
+      <c r="N66" s="65"/>
+      <c r="O66" s="65"/>
+      <c r="P66" s="65"/>
+      <c r="Q66" s="65"/>
     </row>
     <row r="67" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
-      <c r="H67" s="67"/>
-      <c r="I67" s="67"/>
-      <c r="J67" s="67"/>
-      <c r="K67" s="67"/>
-      <c r="L67" s="67"/>
-      <c r="M67" s="67"/>
-      <c r="N67" s="67"/>
-      <c r="O67" s="67"/>
-      <c r="P67" s="67"/>
-      <c r="Q67" s="67"/>
+      <c r="D67" s="65"/>
+      <c r="E67" s="65"/>
+      <c r="F67" s="65"/>
+      <c r="G67" s="65"/>
+      <c r="H67" s="65"/>
+      <c r="I67" s="65"/>
+      <c r="J67" s="65"/>
+      <c r="K67" s="65"/>
+      <c r="L67" s="65"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="65"/>
+      <c r="O67" s="65"/>
+      <c r="P67" s="65"/>
+      <c r="Q67" s="65"/>
     </row>
     <row r="68" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
-      <c r="H68" s="67"/>
-      <c r="I68" s="67"/>
-      <c r="J68" s="67"/>
-      <c r="K68" s="67"/>
-      <c r="L68" s="67"/>
-      <c r="M68" s="67"/>
-      <c r="N68" s="67"/>
-      <c r="O68" s="67"/>
-      <c r="P68" s="67"/>
-      <c r="Q68" s="67"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="65"/>
+      <c r="F68" s="65"/>
+      <c r="G68" s="65"/>
+      <c r="H68" s="65"/>
+      <c r="I68" s="65"/>
+      <c r="J68" s="65"/>
+      <c r="K68" s="65"/>
+      <c r="L68" s="65"/>
+      <c r="M68" s="65"/>
+      <c r="N68" s="65"/>
+      <c r="O68" s="65"/>
+      <c r="P68" s="65"/>
+      <c r="Q68" s="65"/>
     </row>
     <row r="69" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="67"/>
-      <c r="I69" s="67"/>
-      <c r="J69" s="67"/>
-      <c r="K69" s="67"/>
-      <c r="L69" s="67"/>
-      <c r="M69" s="67"/>
-      <c r="N69" s="67"/>
-      <c r="O69" s="67"/>
-      <c r="P69" s="67"/>
-      <c r="Q69" s="67"/>
+      <c r="D69" s="65"/>
+      <c r="E69" s="65"/>
+      <c r="F69" s="65"/>
+      <c r="G69" s="65"/>
+      <c r="H69" s="65"/>
+      <c r="I69" s="65"/>
+      <c r="J69" s="65"/>
+      <c r="K69" s="65"/>
+      <c r="L69" s="65"/>
+      <c r="M69" s="65"/>
+      <c r="N69" s="65"/>
+      <c r="O69" s="65"/>
+      <c r="P69" s="65"/>
+      <c r="Q69" s="65"/>
     </row>
     <row r="70" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D70" s="67"/>
-      <c r="E70" s="67"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="67"/>
-      <c r="I70" s="67"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="67"/>
-      <c r="L70" s="67"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="67"/>
-      <c r="O70" s="67"/>
-      <c r="P70" s="67"/>
-      <c r="Q70" s="67"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="65"/>
+      <c r="H70" s="65"/>
+      <c r="I70" s="65"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="65"/>
+      <c r="L70" s="65"/>
+      <c r="M70" s="65"/>
+      <c r="N70" s="65"/>
+      <c r="O70" s="65"/>
+      <c r="P70" s="65"/>
+      <c r="Q70" s="65"/>
     </row>
     <row r="71" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D71" s="67"/>
-      <c r="E71" s="67"/>
-      <c r="F71" s="67"/>
-      <c r="G71" s="67"/>
-      <c r="H71" s="67"/>
-      <c r="I71" s="67"/>
-      <c r="J71" s="67"/>
-      <c r="K71" s="67"/>
-      <c r="L71" s="67"/>
-      <c r="M71" s="67"/>
-      <c r="N71" s="67"/>
-      <c r="O71" s="67"/>
-      <c r="P71" s="67"/>
-      <c r="Q71" s="67"/>
+      <c r="D71" s="65"/>
+      <c r="E71" s="65"/>
+      <c r="F71" s="65"/>
+      <c r="G71" s="65"/>
+      <c r="H71" s="65"/>
+      <c r="I71" s="65"/>
+      <c r="J71" s="65"/>
+      <c r="K71" s="65"/>
+      <c r="L71" s="65"/>
+      <c r="M71" s="65"/>
+      <c r="N71" s="65"/>
+      <c r="O71" s="65"/>
+      <c r="P71" s="65"/>
+      <c r="Q71" s="65"/>
     </row>
     <row r="72" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D72" s="67"/>
-      <c r="E72" s="67"/>
-      <c r="F72" s="67"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="67"/>
-      <c r="I72" s="67"/>
-      <c r="J72" s="67"/>
-      <c r="K72" s="67"/>
-      <c r="L72" s="67"/>
-      <c r="M72" s="67"/>
-      <c r="N72" s="67"/>
-      <c r="O72" s="67"/>
-      <c r="P72" s="67"/>
-      <c r="Q72" s="67"/>
+      <c r="D72" s="65"/>
+      <c r="E72" s="65"/>
+      <c r="F72" s="65"/>
+      <c r="G72" s="65"/>
+      <c r="H72" s="65"/>
+      <c r="I72" s="65"/>
+      <c r="J72" s="65"/>
+      <c r="K72" s="65"/>
+      <c r="L72" s="65"/>
+      <c r="M72" s="65"/>
+      <c r="N72" s="65"/>
+      <c r="O72" s="65"/>
+      <c r="P72" s="65"/>
+      <c r="Q72" s="65"/>
     </row>
     <row r="73" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D73" s="67"/>
-      <c r="E73" s="67"/>
-      <c r="F73" s="67"/>
-      <c r="G73" s="67"/>
-      <c r="H73" s="67"/>
-      <c r="I73" s="67"/>
-      <c r="J73" s="67"/>
-      <c r="K73" s="67"/>
-      <c r="L73" s="67"/>
-      <c r="M73" s="67"/>
-      <c r="N73" s="67"/>
-      <c r="O73" s="67"/>
-      <c r="P73" s="67"/>
-      <c r="Q73" s="67"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="65"/>
+      <c r="F73" s="65"/>
+      <c r="G73" s="65"/>
+      <c r="H73" s="65"/>
+      <c r="I73" s="65"/>
+      <c r="J73" s="65"/>
+      <c r="K73" s="65"/>
+      <c r="L73" s="65"/>
+      <c r="M73" s="65"/>
+      <c r="N73" s="65"/>
+      <c r="O73" s="65"/>
+      <c r="P73" s="65"/>
+      <c r="Q73" s="65"/>
     </row>
     <row r="74" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D74" s="67"/>
-      <c r="E74" s="67"/>
-      <c r="F74" s="67"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="67"/>
-      <c r="I74" s="67"/>
-      <c r="J74" s="67"/>
-      <c r="K74" s="67"/>
-      <c r="L74" s="67"/>
-      <c r="M74" s="67"/>
-      <c r="N74" s="67"/>
-      <c r="O74" s="67"/>
-      <c r="P74" s="67"/>
-      <c r="Q74" s="67"/>
+      <c r="D74" s="65"/>
+      <c r="E74" s="65"/>
+      <c r="F74" s="65"/>
+      <c r="G74" s="65"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="65"/>
+      <c r="J74" s="65"/>
+      <c r="K74" s="65"/>
+      <c r="L74" s="65"/>
+      <c r="M74" s="65"/>
+      <c r="N74" s="65"/>
+      <c r="O74" s="65"/>
+      <c r="P74" s="65"/>
+      <c r="Q74" s="65"/>
     </row>
     <row r="75" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D75" s="67"/>
-      <c r="E75" s="67"/>
-      <c r="F75" s="67"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="67"/>
-      <c r="I75" s="67"/>
-      <c r="J75" s="67"/>
-      <c r="K75" s="67"/>
-      <c r="L75" s="67"/>
-      <c r="M75" s="67"/>
-      <c r="N75" s="67"/>
-      <c r="O75" s="67"/>
-      <c r="P75" s="67"/>
-      <c r="Q75" s="67"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="65"/>
+      <c r="F75" s="65"/>
+      <c r="G75" s="65"/>
+      <c r="H75" s="65"/>
+      <c r="I75" s="65"/>
+      <c r="J75" s="65"/>
+      <c r="K75" s="65"/>
+      <c r="L75" s="65"/>
+      <c r="M75" s="65"/>
+      <c r="N75" s="65"/>
+      <c r="O75" s="65"/>
+      <c r="P75" s="65"/>
+      <c r="Q75" s="65"/>
     </row>
     <row r="76" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D76" s="67"/>
-      <c r="E76" s="67"/>
-      <c r="F76" s="67"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="67"/>
-      <c r="I76" s="67"/>
-      <c r="J76" s="67"/>
-      <c r="K76" s="67"/>
-      <c r="L76" s="67"/>
-      <c r="M76" s="67"/>
-      <c r="N76" s="67"/>
-      <c r="O76" s="67"/>
-      <c r="P76" s="67"/>
-      <c r="Q76" s="67"/>
+      <c r="D76" s="65"/>
+      <c r="E76" s="65"/>
+      <c r="F76" s="65"/>
+      <c r="G76" s="65"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="65"/>
+      <c r="J76" s="65"/>
+      <c r="K76" s="65"/>
+      <c r="L76" s="65"/>
+      <c r="M76" s="65"/>
+      <c r="N76" s="65"/>
+      <c r="O76" s="65"/>
+      <c r="P76" s="65"/>
+      <c r="Q76" s="65"/>
     </row>
     <row r="77" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D77" s="67"/>
-      <c r="E77" s="67"/>
-      <c r="F77" s="67"/>
-      <c r="G77" s="67"/>
-      <c r="H77" s="67"/>
-      <c r="I77" s="67"/>
-      <c r="J77" s="67"/>
-      <c r="K77" s="67"/>
-      <c r="L77" s="67"/>
-      <c r="M77" s="67"/>
-      <c r="N77" s="67"/>
-      <c r="O77" s="67"/>
-      <c r="P77" s="67"/>
-      <c r="Q77" s="67"/>
+      <c r="D77" s="65"/>
+      <c r="E77" s="65"/>
+      <c r="F77" s="65"/>
+      <c r="G77" s="65"/>
+      <c r="H77" s="65"/>
+      <c r="I77" s="65"/>
+      <c r="J77" s="65"/>
+      <c r="K77" s="65"/>
+      <c r="L77" s="65"/>
+      <c r="M77" s="65"/>
+      <c r="N77" s="65"/>
+      <c r="O77" s="65"/>
+      <c r="P77" s="65"/>
+      <c r="Q77" s="65"/>
     </row>
     <row r="78" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D78" s="67"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="67"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="67"/>
-      <c r="I78" s="67"/>
-      <c r="J78" s="67"/>
-      <c r="K78" s="67"/>
-      <c r="L78" s="67"/>
-      <c r="M78" s="67"/>
-      <c r="N78" s="67"/>
-      <c r="O78" s="67"/>
-      <c r="P78" s="67"/>
-      <c r="Q78" s="67"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="65"/>
+      <c r="H78" s="65"/>
+      <c r="I78" s="65"/>
+      <c r="J78" s="65"/>
+      <c r="K78" s="65"/>
+      <c r="L78" s="65"/>
+      <c r="M78" s="65"/>
+      <c r="N78" s="65"/>
+      <c r="O78" s="65"/>
+      <c r="P78" s="65"/>
+      <c r="Q78" s="65"/>
     </row>
     <row r="79" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D79" s="67"/>
-      <c r="E79" s="67"/>
-      <c r="F79" s="67"/>
-      <c r="G79" s="67"/>
-      <c r="H79" s="67"/>
-      <c r="I79" s="67"/>
-      <c r="J79" s="67"/>
-      <c r="K79" s="67"/>
-      <c r="L79" s="67"/>
-      <c r="M79" s="67"/>
-      <c r="N79" s="67"/>
-      <c r="O79" s="67"/>
-      <c r="P79" s="67"/>
-      <c r="Q79" s="67"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="65"/>
+      <c r="F79" s="65"/>
+      <c r="G79" s="65"/>
+      <c r="H79" s="65"/>
+      <c r="I79" s="65"/>
+      <c r="J79" s="65"/>
+      <c r="K79" s="65"/>
+      <c r="L79" s="65"/>
+      <c r="M79" s="65"/>
+      <c r="N79" s="65"/>
+      <c r="O79" s="65"/>
+      <c r="P79" s="65"/>
+      <c r="Q79" s="65"/>
     </row>
     <row r="80" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="67"/>
-      <c r="J80" s="67"/>
-      <c r="K80" s="67"/>
-      <c r="L80" s="67"/>
-      <c r="M80" s="67"/>
-      <c r="N80" s="67"/>
-      <c r="O80" s="67"/>
-      <c r="P80" s="67"/>
-      <c r="Q80" s="67"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="65"/>
+      <c r="J80" s="65"/>
+      <c r="K80" s="65"/>
+      <c r="L80" s="65"/>
+      <c r="M80" s="65"/>
+      <c r="N80" s="65"/>
+      <c r="O80" s="65"/>
+      <c r="P80" s="65"/>
+      <c r="Q80" s="65"/>
     </row>
     <row r="81" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="67"/>
-      <c r="G81" s="67"/>
-      <c r="H81" s="67"/>
-      <c r="I81" s="67"/>
-      <c r="J81" s="67"/>
-      <c r="K81" s="67"/>
-      <c r="L81" s="67"/>
-      <c r="M81" s="67"/>
-      <c r="N81" s="67"/>
-      <c r="O81" s="67"/>
-      <c r="P81" s="67"/>
-      <c r="Q81" s="67"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="65"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
+      <c r="N81" s="65"/>
+      <c r="O81" s="65"/>
+      <c r="P81" s="65"/>
+      <c r="Q81" s="65"/>
     </row>
     <row r="82" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D82" s="67"/>
-      <c r="E82" s="67"/>
-      <c r="F82" s="67"/>
-      <c r="G82" s="67"/>
-      <c r="H82" s="67"/>
-      <c r="I82" s="67"/>
-      <c r="J82" s="67"/>
-      <c r="K82" s="67"/>
-      <c r="L82" s="67"/>
-      <c r="M82" s="67"/>
-      <c r="N82" s="67"/>
-      <c r="O82" s="67"/>
-      <c r="P82" s="67"/>
-      <c r="Q82" s="67"/>
+      <c r="D82" s="65"/>
+      <c r="E82" s="65"/>
+      <c r="F82" s="65"/>
+      <c r="G82" s="65"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="65"/>
+      <c r="J82" s="65"/>
+      <c r="K82" s="65"/>
+      <c r="L82" s="65"/>
+      <c r="M82" s="65"/>
+      <c r="N82" s="65"/>
+      <c r="O82" s="65"/>
+      <c r="P82" s="65"/>
+      <c r="Q82" s="65"/>
     </row>
     <row r="83" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D83" s="67"/>
-      <c r="E83" s="67"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="67"/>
-      <c r="H83" s="67"/>
-      <c r="I83" s="67"/>
-      <c r="J83" s="67"/>
-      <c r="K83" s="67"/>
-      <c r="L83" s="67"/>
-      <c r="M83" s="67"/>
-      <c r="N83" s="67"/>
-      <c r="O83" s="67"/>
-      <c r="P83" s="67"/>
-      <c r="Q83" s="67"/>
+      <c r="D83" s="65"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="65"/>
+      <c r="I83" s="65"/>
+      <c r="J83" s="65"/>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
+      <c r="M83" s="65"/>
+      <c r="N83" s="65"/>
+      <c r="O83" s="65"/>
+      <c r="P83" s="65"/>
+      <c r="Q83" s="65"/>
     </row>
     <row r="84" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D84" s="67"/>
-      <c r="E84" s="67"/>
-      <c r="F84" s="67"/>
-      <c r="G84" s="67"/>
-      <c r="H84" s="67"/>
-      <c r="I84" s="67"/>
-      <c r="J84" s="67"/>
-      <c r="K84" s="67"/>
-      <c r="L84" s="67"/>
-      <c r="M84" s="67"/>
-      <c r="N84" s="67"/>
-      <c r="O84" s="67"/>
-      <c r="P84" s="67"/>
-      <c r="Q84" s="67"/>
+      <c r="D84" s="65"/>
+      <c r="E84" s="65"/>
+      <c r="F84" s="65"/>
+      <c r="G84" s="65"/>
+      <c r="H84" s="65"/>
+      <c r="I84" s="65"/>
+      <c r="J84" s="65"/>
+      <c r="K84" s="65"/>
+      <c r="L84" s="65"/>
+      <c r="M84" s="65"/>
+      <c r="N84" s="65"/>
+      <c r="O84" s="65"/>
+      <c r="P84" s="65"/>
+      <c r="Q84" s="65"/>
     </row>
     <row r="85" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D85" s="67"/>
-      <c r="E85" s="67"/>
-      <c r="F85" s="67"/>
-      <c r="G85" s="67"/>
-      <c r="H85" s="67"/>
-      <c r="I85" s="67"/>
-      <c r="J85" s="67"/>
-      <c r="K85" s="67"/>
-      <c r="L85" s="67"/>
-      <c r="M85" s="67"/>
-      <c r="N85" s="67"/>
-      <c r="O85" s="67"/>
-      <c r="P85" s="67"/>
-      <c r="Q85" s="67"/>
+      <c r="D85" s="65"/>
+      <c r="E85" s="65"/>
+      <c r="F85" s="65"/>
+      <c r="G85" s="65"/>
+      <c r="H85" s="65"/>
+      <c r="I85" s="65"/>
+      <c r="J85" s="65"/>
+      <c r="K85" s="65"/>
+      <c r="L85" s="65"/>
+      <c r="M85" s="65"/>
+      <c r="N85" s="65"/>
+      <c r="O85" s="65"/>
+      <c r="P85" s="65"/>
+      <c r="Q85" s="65"/>
     </row>
     <row r="86" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="67"/>
-      <c r="G86" s="67"/>
-      <c r="H86" s="67"/>
-      <c r="I86" s="67"/>
-      <c r="J86" s="67"/>
-      <c r="K86" s="67"/>
-      <c r="L86" s="67"/>
-      <c r="M86" s="67"/>
-      <c r="N86" s="67"/>
-      <c r="O86" s="67"/>
-      <c r="P86" s="67"/>
-      <c r="Q86" s="67"/>
+      <c r="D86" s="65"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="65"/>
+      <c r="G86" s="65"/>
+      <c r="H86" s="65"/>
+      <c r="I86" s="65"/>
+      <c r="J86" s="65"/>
+      <c r="K86" s="65"/>
+      <c r="L86" s="65"/>
+      <c r="M86" s="65"/>
+      <c r="N86" s="65"/>
+      <c r="O86" s="65"/>
+      <c r="P86" s="65"/>
+      <c r="Q86" s="65"/>
     </row>
     <row r="87" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
-      <c r="H87" s="67"/>
-      <c r="I87" s="67"/>
-      <c r="J87" s="67"/>
-      <c r="K87" s="67"/>
-      <c r="L87" s="67"/>
-      <c r="M87" s="67"/>
-      <c r="N87" s="67"/>
-      <c r="O87" s="67"/>
-      <c r="P87" s="67"/>
-      <c r="Q87" s="67"/>
+      <c r="D87" s="65"/>
+      <c r="E87" s="65"/>
+      <c r="F87" s="65"/>
+      <c r="G87" s="65"/>
+      <c r="H87" s="65"/>
+      <c r="I87" s="65"/>
+      <c r="J87" s="65"/>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
+      <c r="M87" s="65"/>
+      <c r="N87" s="65"/>
+      <c r="O87" s="65"/>
+      <c r="P87" s="65"/>
+      <c r="Q87" s="65"/>
     </row>
     <row r="88" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D88" s="67"/>
-      <c r="E88" s="67"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="67"/>
-      <c r="H88" s="67"/>
-      <c r="I88" s="67"/>
-      <c r="J88" s="67"/>
-      <c r="K88" s="67"/>
-      <c r="L88" s="67"/>
-      <c r="M88" s="67"/>
-      <c r="N88" s="67"/>
-      <c r="O88" s="67"/>
-      <c r="P88" s="67"/>
-      <c r="Q88" s="67"/>
+      <c r="D88" s="65"/>
+      <c r="E88" s="65"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="65"/>
+      <c r="H88" s="65"/>
+      <c r="I88" s="65"/>
+      <c r="J88" s="65"/>
+      <c r="K88" s="65"/>
+      <c r="L88" s="65"/>
+      <c r="M88" s="65"/>
+      <c r="N88" s="65"/>
+      <c r="O88" s="65"/>
+      <c r="P88" s="65"/>
+      <c r="Q88" s="65"/>
     </row>
     <row r="89" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D89" s="67"/>
-      <c r="E89" s="67"/>
-      <c r="F89" s="67"/>
-      <c r="G89" s="67"/>
-      <c r="H89" s="67"/>
-      <c r="I89" s="67"/>
-      <c r="J89" s="67"/>
-      <c r="K89" s="67"/>
-      <c r="L89" s="67"/>
-      <c r="M89" s="67"/>
-      <c r="N89" s="67"/>
-      <c r="O89" s="67"/>
-      <c r="P89" s="67"/>
-      <c r="Q89" s="67"/>
+      <c r="D89" s="65"/>
+      <c r="E89" s="65"/>
+      <c r="F89" s="65"/>
+      <c r="G89" s="65"/>
+      <c r="H89" s="65"/>
+      <c r="I89" s="65"/>
+      <c r="J89" s="65"/>
+      <c r="K89" s="65"/>
+      <c r="L89" s="65"/>
+      <c r="M89" s="65"/>
+      <c r="N89" s="65"/>
+      <c r="O89" s="65"/>
+      <c r="P89" s="65"/>
+      <c r="Q89" s="65"/>
     </row>
     <row r="90" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
-      <c r="H90" s="67"/>
-      <c r="I90" s="67"/>
-      <c r="J90" s="67"/>
-      <c r="K90" s="67"/>
-      <c r="L90" s="67"/>
-      <c r="M90" s="67"/>
-      <c r="N90" s="67"/>
-      <c r="O90" s="67"/>
-      <c r="P90" s="67"/>
-      <c r="Q90" s="67"/>
+      <c r="D90" s="65"/>
+      <c r="E90" s="65"/>
+      <c r="F90" s="65"/>
+      <c r="G90" s="65"/>
+      <c r="H90" s="65"/>
+      <c r="I90" s="65"/>
+      <c r="J90" s="65"/>
+      <c r="K90" s="65"/>
+      <c r="L90" s="65"/>
+      <c r="M90" s="65"/>
+      <c r="N90" s="65"/>
+      <c r="O90" s="65"/>
+      <c r="P90" s="65"/>
+      <c r="Q90" s="65"/>
     </row>
     <row r="91" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D91" s="67"/>
-      <c r="E91" s="67"/>
-      <c r="F91" s="67"/>
-      <c r="G91" s="67"/>
-      <c r="H91" s="67"/>
-      <c r="I91" s="67"/>
-      <c r="J91" s="67"/>
-      <c r="K91" s="67"/>
-      <c r="L91" s="67"/>
-      <c r="M91" s="67"/>
-      <c r="N91" s="67"/>
-      <c r="O91" s="67"/>
-      <c r="P91" s="67"/>
-      <c r="Q91" s="67"/>
+      <c r="D91" s="65"/>
+      <c r="E91" s="65"/>
+      <c r="F91" s="65"/>
+      <c r="G91" s="65"/>
+      <c r="H91" s="65"/>
+      <c r="I91" s="65"/>
+      <c r="J91" s="65"/>
+      <c r="K91" s="65"/>
+      <c r="L91" s="65"/>
+      <c r="M91" s="65"/>
+      <c r="N91" s="65"/>
+      <c r="O91" s="65"/>
+      <c r="P91" s="65"/>
+      <c r="Q91" s="65"/>
     </row>
     <row r="92" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D92" s="67"/>
-      <c r="E92" s="67"/>
-      <c r="F92" s="67"/>
-      <c r="G92" s="67"/>
-      <c r="H92" s="67"/>
-      <c r="I92" s="67"/>
-      <c r="J92" s="67"/>
-      <c r="K92" s="67"/>
-      <c r="L92" s="67"/>
-      <c r="M92" s="67"/>
-      <c r="N92" s="67"/>
-      <c r="O92" s="67"/>
-      <c r="P92" s="67"/>
-      <c r="Q92" s="67"/>
+      <c r="D92" s="65"/>
+      <c r="E92" s="65"/>
+      <c r="F92" s="65"/>
+      <c r="G92" s="65"/>
+      <c r="H92" s="65"/>
+      <c r="I92" s="65"/>
+      <c r="J92" s="65"/>
+      <c r="K92" s="65"/>
+      <c r="L92" s="65"/>
+      <c r="M92" s="65"/>
+      <c r="N92" s="65"/>
+      <c r="O92" s="65"/>
+      <c r="P92" s="65"/>
+      <c r="Q92" s="65"/>
     </row>
     <row r="93" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="67"/>
-      <c r="H93" s="67"/>
-      <c r="I93" s="67"/>
-      <c r="J93" s="67"/>
-      <c r="K93" s="67"/>
-      <c r="L93" s="67"/>
-      <c r="M93" s="67"/>
-      <c r="N93" s="67"/>
-      <c r="O93" s="67"/>
-      <c r="P93" s="67"/>
-      <c r="Q93" s="67"/>
+      <c r="D93" s="65"/>
+      <c r="E93" s="65"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="65"/>
+      <c r="H93" s="65"/>
+      <c r="I93" s="65"/>
+      <c r="J93" s="65"/>
+      <c r="K93" s="65"/>
+      <c r="L93" s="65"/>
+      <c r="M93" s="65"/>
+      <c r="N93" s="65"/>
+      <c r="O93" s="65"/>
+      <c r="P93" s="65"/>
+      <c r="Q93" s="65"/>
     </row>
     <row r="94" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D94" s="67"/>
-      <c r="E94" s="67"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="67"/>
-      <c r="H94" s="67"/>
-      <c r="I94" s="67"/>
-      <c r="J94" s="67"/>
-      <c r="K94" s="67"/>
-      <c r="L94" s="67"/>
-      <c r="M94" s="67"/>
-      <c r="N94" s="67"/>
-      <c r="O94" s="67"/>
-      <c r="P94" s="67"/>
-      <c r="Q94" s="67"/>
+      <c r="D94" s="65"/>
+      <c r="E94" s="65"/>
+      <c r="F94" s="65"/>
+      <c r="G94" s="65"/>
+      <c r="H94" s="65"/>
+      <c r="I94" s="65"/>
+      <c r="J94" s="65"/>
+      <c r="K94" s="65"/>
+      <c r="L94" s="65"/>
+      <c r="M94" s="65"/>
+      <c r="N94" s="65"/>
+      <c r="O94" s="65"/>
+      <c r="P94" s="65"/>
+      <c r="Q94" s="65"/>
     </row>
     <row r="95" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
-      <c r="F95" s="67"/>
-      <c r="G95" s="67"/>
-      <c r="H95" s="67"/>
-      <c r="I95" s="67"/>
-      <c r="J95" s="67"/>
-      <c r="K95" s="67"/>
-      <c r="L95" s="67"/>
-      <c r="M95" s="67"/>
-      <c r="N95" s="67"/>
-      <c r="O95" s="67"/>
-      <c r="P95" s="67"/>
-      <c r="Q95" s="67"/>
+      <c r="D95" s="65"/>
+      <c r="E95" s="65"/>
+      <c r="F95" s="65"/>
+      <c r="G95" s="65"/>
+      <c r="H95" s="65"/>
+      <c r="I95" s="65"/>
+      <c r="J95" s="65"/>
+      <c r="K95" s="65"/>
+      <c r="L95" s="65"/>
+      <c r="M95" s="65"/>
+      <c r="N95" s="65"/>
+      <c r="O95" s="65"/>
+      <c r="P95" s="65"/>
+      <c r="Q95" s="65"/>
     </row>
     <row r="96" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D96" s="67"/>
-      <c r="E96" s="67"/>
-      <c r="F96" s="67"/>
-      <c r="G96" s="67"/>
-      <c r="H96" s="67"/>
-      <c r="I96" s="67"/>
-      <c r="J96" s="67"/>
-      <c r="K96" s="67"/>
-      <c r="L96" s="67"/>
-      <c r="M96" s="67"/>
-      <c r="N96" s="67"/>
-      <c r="O96" s="67"/>
-      <c r="P96" s="67"/>
-      <c r="Q96" s="67"/>
+      <c r="D96" s="65"/>
+      <c r="E96" s="65"/>
+      <c r="F96" s="65"/>
+      <c r="G96" s="65"/>
+      <c r="H96" s="65"/>
+      <c r="I96" s="65"/>
+      <c r="J96" s="65"/>
+      <c r="K96" s="65"/>
+      <c r="L96" s="65"/>
+      <c r="M96" s="65"/>
+      <c r="N96" s="65"/>
+      <c r="O96" s="65"/>
+      <c r="P96" s="65"/>
+      <c r="Q96" s="65"/>
     </row>
     <row r="97" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D97" s="67"/>
-      <c r="E97" s="67"/>
-      <c r="F97" s="67"/>
-      <c r="G97" s="67"/>
-      <c r="H97" s="67"/>
-      <c r="I97" s="67"/>
-      <c r="J97" s="67"/>
-      <c r="K97" s="67"/>
-      <c r="L97" s="67"/>
-      <c r="M97" s="67"/>
-      <c r="N97" s="67"/>
-      <c r="O97" s="67"/>
-      <c r="P97" s="67"/>
-      <c r="Q97" s="67"/>
+      <c r="D97" s="65"/>
+      <c r="E97" s="65"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="65"/>
+      <c r="H97" s="65"/>
+      <c r="I97" s="65"/>
+      <c r="J97" s="65"/>
+      <c r="K97" s="65"/>
+      <c r="L97" s="65"/>
+      <c r="M97" s="65"/>
+      <c r="N97" s="65"/>
+      <c r="O97" s="65"/>
+      <c r="P97" s="65"/>
+      <c r="Q97" s="65"/>
     </row>
     <row r="98" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="67"/>
-      <c r="G98" s="67"/>
-      <c r="H98" s="67"/>
-      <c r="I98" s="67"/>
-      <c r="J98" s="67"/>
-      <c r="K98" s="67"/>
-      <c r="L98" s="67"/>
-      <c r="M98" s="67"/>
-      <c r="N98" s="67"/>
-      <c r="O98" s="67"/>
-      <c r="P98" s="67"/>
-      <c r="Q98" s="67"/>
+      <c r="D98" s="65"/>
+      <c r="E98" s="65"/>
+      <c r="F98" s="65"/>
+      <c r="G98" s="65"/>
+      <c r="H98" s="65"/>
+      <c r="I98" s="65"/>
+      <c r="J98" s="65"/>
+      <c r="K98" s="65"/>
+      <c r="L98" s="65"/>
+      <c r="M98" s="65"/>
+      <c r="N98" s="65"/>
+      <c r="O98" s="65"/>
+      <c r="P98" s="65"/>
+      <c r="Q98" s="65"/>
     </row>
     <row r="99" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D99" s="67"/>
-      <c r="E99" s="67"/>
-      <c r="F99" s="67"/>
-      <c r="G99" s="67"/>
-      <c r="H99" s="67"/>
-      <c r="I99" s="67"/>
-      <c r="J99" s="67"/>
-      <c r="K99" s="67"/>
-      <c r="L99" s="67"/>
-      <c r="M99" s="67"/>
-      <c r="N99" s="67"/>
-      <c r="O99" s="67"/>
-      <c r="P99" s="67"/>
-      <c r="Q99" s="67"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
+      <c r="H99" s="65"/>
+      <c r="I99" s="65"/>
+      <c r="J99" s="65"/>
+      <c r="K99" s="65"/>
+      <c r="L99" s="65"/>
+      <c r="M99" s="65"/>
+      <c r="N99" s="65"/>
+      <c r="O99" s="65"/>
+      <c r="P99" s="65"/>
+      <c r="Q99" s="65"/>
     </row>
     <row r="100" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D100" s="67"/>
-      <c r="E100" s="67"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="67"/>
-      <c r="H100" s="67"/>
-      <c r="I100" s="67"/>
-      <c r="J100" s="67"/>
-      <c r="K100" s="67"/>
-      <c r="L100" s="67"/>
-      <c r="M100" s="67"/>
-      <c r="N100" s="67"/>
-      <c r="O100" s="67"/>
-      <c r="P100" s="67"/>
-      <c r="Q100" s="67"/>
+      <c r="D100" s="65"/>
+      <c r="E100" s="65"/>
+      <c r="F100" s="65"/>
+      <c r="G100" s="65"/>
+      <c r="H100" s="65"/>
+      <c r="I100" s="65"/>
+      <c r="J100" s="65"/>
+      <c r="K100" s="65"/>
+      <c r="L100" s="65"/>
+      <c r="M100" s="65"/>
+      <c r="N100" s="65"/>
+      <c r="O100" s="65"/>
+      <c r="P100" s="65"/>
+      <c r="Q100" s="65"/>
     </row>
     <row r="101" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D101" s="67"/>
-      <c r="E101" s="67"/>
-      <c r="F101" s="67"/>
-      <c r="G101" s="67"/>
-      <c r="H101" s="67"/>
-      <c r="I101" s="67"/>
-      <c r="J101" s="67"/>
-      <c r="K101" s="67"/>
-      <c r="L101" s="67"/>
-      <c r="M101" s="67"/>
-      <c r="N101" s="67"/>
-      <c r="O101" s="67"/>
-      <c r="P101" s="67"/>
-      <c r="Q101" s="67"/>
+      <c r="D101" s="65"/>
+      <c r="E101" s="65"/>
+      <c r="F101" s="65"/>
+      <c r="G101" s="65"/>
+      <c r="H101" s="65"/>
+      <c r="I101" s="65"/>
+      <c r="J101" s="65"/>
+      <c r="K101" s="65"/>
+      <c r="L101" s="65"/>
+      <c r="M101" s="65"/>
+      <c r="N101" s="65"/>
+      <c r="O101" s="65"/>
+      <c r="P101" s="65"/>
+      <c r="Q101" s="65"/>
     </row>
     <row r="102" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D102" s="67"/>
-      <c r="E102" s="67"/>
-      <c r="F102" s="67"/>
-      <c r="G102" s="67"/>
-      <c r="H102" s="67"/>
-      <c r="I102" s="67"/>
-      <c r="J102" s="67"/>
-      <c r="K102" s="67"/>
-      <c r="L102" s="67"/>
-      <c r="M102" s="67"/>
-      <c r="N102" s="67"/>
-      <c r="O102" s="67"/>
-      <c r="P102" s="67"/>
-      <c r="Q102" s="67"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="65"/>
+      <c r="G102" s="65"/>
+      <c r="H102" s="65"/>
+      <c r="I102" s="65"/>
+      <c r="J102" s="65"/>
+      <c r="K102" s="65"/>
+      <c r="L102" s="65"/>
+      <c r="M102" s="65"/>
+      <c r="N102" s="65"/>
+      <c r="O102" s="65"/>
+      <c r="P102" s="65"/>
+      <c r="Q102" s="65"/>
     </row>
     <row r="103" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D103" s="67"/>
-      <c r="E103" s="67"/>
-      <c r="F103" s="67"/>
-      <c r="G103" s="67"/>
-      <c r="H103" s="67"/>
-      <c r="I103" s="67"/>
-      <c r="J103" s="67"/>
-      <c r="K103" s="67"/>
-      <c r="L103" s="67"/>
-      <c r="M103" s="67"/>
-      <c r="N103" s="67"/>
-      <c r="O103" s="67"/>
-      <c r="P103" s="67"/>
-      <c r="Q103" s="67"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="65"/>
+      <c r="G103" s="65"/>
+      <c r="H103" s="65"/>
+      <c r="I103" s="65"/>
+      <c r="J103" s="65"/>
+      <c r="K103" s="65"/>
+      <c r="L103" s="65"/>
+      <c r="M103" s="65"/>
+      <c r="N103" s="65"/>
+      <c r="O103" s="65"/>
+      <c r="P103" s="65"/>
+      <c r="Q103" s="65"/>
     </row>
     <row r="104" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
-      <c r="H104" s="67"/>
-      <c r="I104" s="67"/>
-      <c r="J104" s="67"/>
-      <c r="K104" s="67"/>
-      <c r="L104" s="67"/>
-      <c r="M104" s="67"/>
-      <c r="N104" s="67"/>
-      <c r="O104" s="67"/>
-      <c r="P104" s="67"/>
-      <c r="Q104" s="67"/>
+      <c r="D104" s="65"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="65"/>
+      <c r="G104" s="65"/>
+      <c r="H104" s="65"/>
+      <c r="I104" s="65"/>
+      <c r="J104" s="65"/>
+      <c r="K104" s="65"/>
+      <c r="L104" s="65"/>
+      <c r="M104" s="65"/>
+      <c r="N104" s="65"/>
+      <c r="O104" s="65"/>
+      <c r="P104" s="65"/>
+      <c r="Q104" s="65"/>
     </row>
     <row r="105" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D105" s="67"/>
-      <c r="E105" s="67"/>
-      <c r="F105" s="67"/>
-      <c r="G105" s="67"/>
-      <c r="H105" s="67"/>
-      <c r="I105" s="67"/>
-      <c r="J105" s="67"/>
-      <c r="K105" s="67"/>
-      <c r="L105" s="67"/>
-      <c r="M105" s="67"/>
-      <c r="N105" s="67"/>
-      <c r="O105" s="67"/>
-      <c r="P105" s="67"/>
-      <c r="Q105" s="67"/>
+      <c r="D105" s="65"/>
+      <c r="E105" s="65"/>
+      <c r="F105" s="65"/>
+      <c r="G105" s="65"/>
+      <c r="H105" s="65"/>
+      <c r="I105" s="65"/>
+      <c r="J105" s="65"/>
+      <c r="K105" s="65"/>
+      <c r="L105" s="65"/>
+      <c r="M105" s="65"/>
+      <c r="N105" s="65"/>
+      <c r="O105" s="65"/>
+      <c r="P105" s="65"/>
+      <c r="Q105" s="65"/>
     </row>
     <row r="106" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D106" s="67"/>
-      <c r="E106" s="67"/>
-      <c r="F106" s="67"/>
-      <c r="G106" s="67"/>
-      <c r="H106" s="67"/>
-      <c r="I106" s="67"/>
-      <c r="J106" s="67"/>
-      <c r="K106" s="67"/>
-      <c r="L106" s="67"/>
-      <c r="M106" s="67"/>
-      <c r="N106" s="67"/>
-      <c r="O106" s="67"/>
-      <c r="P106" s="67"/>
-      <c r="Q106" s="67"/>
+      <c r="D106" s="65"/>
+      <c r="E106" s="65"/>
+      <c r="F106" s="65"/>
+      <c r="G106" s="65"/>
+      <c r="H106" s="65"/>
+      <c r="I106" s="65"/>
+      <c r="J106" s="65"/>
+      <c r="K106" s="65"/>
+      <c r="L106" s="65"/>
+      <c r="M106" s="65"/>
+      <c r="N106" s="65"/>
+      <c r="O106" s="65"/>
+      <c r="P106" s="65"/>
+      <c r="Q106" s="65"/>
     </row>
     <row r="107" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D107" s="67"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="67"/>
-      <c r="G107" s="67"/>
-      <c r="H107" s="67"/>
-      <c r="I107" s="67"/>
-      <c r="J107" s="67"/>
-      <c r="K107" s="67"/>
-      <c r="L107" s="67"/>
-      <c r="M107" s="67"/>
-      <c r="N107" s="67"/>
-      <c r="O107" s="67"/>
-      <c r="P107" s="67"/>
-      <c r="Q107" s="67"/>
+      <c r="D107" s="65"/>
+      <c r="E107" s="65"/>
+      <c r="F107" s="65"/>
+      <c r="G107" s="65"/>
+      <c r="H107" s="65"/>
+      <c r="I107" s="65"/>
+      <c r="J107" s="65"/>
+      <c r="K107" s="65"/>
+      <c r="L107" s="65"/>
+      <c r="M107" s="65"/>
+      <c r="N107" s="65"/>
+      <c r="O107" s="65"/>
+      <c r="P107" s="65"/>
+      <c r="Q107" s="65"/>
     </row>
     <row r="108" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D108" s="67"/>
-      <c r="E108" s="67"/>
-      <c r="F108" s="67"/>
-      <c r="G108" s="67"/>
-      <c r="H108" s="67"/>
-      <c r="I108" s="67"/>
-      <c r="J108" s="67"/>
-      <c r="K108" s="67"/>
-      <c r="L108" s="67"/>
-      <c r="M108" s="67"/>
-      <c r="N108" s="67"/>
-      <c r="O108" s="67"/>
-      <c r="P108" s="67"/>
-      <c r="Q108" s="67"/>
+      <c r="D108" s="65"/>
+      <c r="E108" s="65"/>
+      <c r="F108" s="65"/>
+      <c r="G108" s="65"/>
+      <c r="H108" s="65"/>
+      <c r="I108" s="65"/>
+      <c r="J108" s="65"/>
+      <c r="K108" s="65"/>
+      <c r="L108" s="65"/>
+      <c r="M108" s="65"/>
+      <c r="N108" s="65"/>
+      <c r="O108" s="65"/>
+      <c r="P108" s="65"/>
+      <c r="Q108" s="65"/>
     </row>
     <row r="109" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D109" s="67"/>
-      <c r="E109" s="67"/>
-      <c r="F109" s="67"/>
-      <c r="G109" s="67"/>
-      <c r="H109" s="67"/>
-      <c r="I109" s="67"/>
-      <c r="J109" s="67"/>
-      <c r="K109" s="67"/>
-      <c r="L109" s="67"/>
-      <c r="M109" s="67"/>
-      <c r="N109" s="67"/>
-      <c r="O109" s="67"/>
-      <c r="P109" s="67"/>
-      <c r="Q109" s="67"/>
+      <c r="D109" s="65"/>
+      <c r="E109" s="65"/>
+      <c r="F109" s="65"/>
+      <c r="G109" s="65"/>
+      <c r="H109" s="65"/>
+      <c r="I109" s="65"/>
+      <c r="J109" s="65"/>
+      <c r="K109" s="65"/>
+      <c r="L109" s="65"/>
+      <c r="M109" s="65"/>
+      <c r="N109" s="65"/>
+      <c r="O109" s="65"/>
+      <c r="P109" s="65"/>
+      <c r="Q109" s="65"/>
     </row>
     <row r="110" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D110" s="67"/>
-      <c r="E110" s="67"/>
-      <c r="F110" s="67"/>
-      <c r="G110" s="67"/>
-      <c r="H110" s="67"/>
-      <c r="I110" s="67"/>
-      <c r="J110" s="67"/>
-      <c r="K110" s="67"/>
-      <c r="L110" s="67"/>
-      <c r="M110" s="67"/>
-      <c r="N110" s="67"/>
-      <c r="O110" s="67"/>
-      <c r="P110" s="67"/>
-      <c r="Q110" s="67"/>
+      <c r="D110" s="65"/>
+      <c r="E110" s="65"/>
+      <c r="F110" s="65"/>
+      <c r="G110" s="65"/>
+      <c r="H110" s="65"/>
+      <c r="I110" s="65"/>
+      <c r="J110" s="65"/>
+      <c r="K110" s="65"/>
+      <c r="L110" s="65"/>
+      <c r="M110" s="65"/>
+      <c r="N110" s="65"/>
+      <c r="O110" s="65"/>
+      <c r="P110" s="65"/>
+      <c r="Q110" s="65"/>
     </row>
     <row r="111" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D111" s="67"/>
-      <c r="E111" s="67"/>
-      <c r="F111" s="67"/>
-      <c r="G111" s="67"/>
-      <c r="H111" s="67"/>
-      <c r="I111" s="67"/>
-      <c r="J111" s="67"/>
-      <c r="K111" s="67"/>
-      <c r="L111" s="67"/>
-      <c r="M111" s="67"/>
-      <c r="N111" s="67"/>
-      <c r="O111" s="67"/>
-      <c r="P111" s="67"/>
-      <c r="Q111" s="67"/>
+      <c r="D111" s="65"/>
+      <c r="E111" s="65"/>
+      <c r="F111" s="65"/>
+      <c r="G111" s="65"/>
+      <c r="H111" s="65"/>
+      <c r="I111" s="65"/>
+      <c r="J111" s="65"/>
+      <c r="K111" s="65"/>
+      <c r="L111" s="65"/>
+      <c r="M111" s="65"/>
+      <c r="N111" s="65"/>
+      <c r="O111" s="65"/>
+      <c r="P111" s="65"/>
+      <c r="Q111" s="65"/>
     </row>
     <row r="112" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D112" s="67"/>
-      <c r="E112" s="67"/>
-      <c r="F112" s="67"/>
-      <c r="G112" s="67"/>
-      <c r="H112" s="67"/>
-      <c r="I112" s="67"/>
-      <c r="J112" s="67"/>
-      <c r="K112" s="67"/>
-      <c r="L112" s="67"/>
-      <c r="M112" s="67"/>
-      <c r="N112" s="67"/>
-      <c r="O112" s="67"/>
-      <c r="P112" s="67"/>
-      <c r="Q112" s="67"/>
+      <c r="D112" s="65"/>
+      <c r="E112" s="65"/>
+      <c r="F112" s="65"/>
+      <c r="G112" s="65"/>
+      <c r="H112" s="65"/>
+      <c r="I112" s="65"/>
+      <c r="J112" s="65"/>
+      <c r="K112" s="65"/>
+      <c r="L112" s="65"/>
+      <c r="M112" s="65"/>
+      <c r="N112" s="65"/>
+      <c r="O112" s="65"/>
+      <c r="P112" s="65"/>
+      <c r="Q112" s="65"/>
     </row>
     <row r="113" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D113" s="67"/>
-      <c r="E113" s="67"/>
-      <c r="F113" s="67"/>
-      <c r="G113" s="67"/>
-      <c r="H113" s="67"/>
-      <c r="I113" s="67"/>
-      <c r="J113" s="67"/>
-      <c r="K113" s="67"/>
-      <c r="L113" s="67"/>
-      <c r="M113" s="67"/>
-      <c r="N113" s="67"/>
-      <c r="O113" s="67"/>
-      <c r="P113" s="67"/>
-      <c r="Q113" s="67"/>
+      <c r="D113" s="65"/>
+      <c r="E113" s="65"/>
+      <c r="F113" s="65"/>
+      <c r="G113" s="65"/>
+      <c r="H113" s="65"/>
+      <c r="I113" s="65"/>
+      <c r="J113" s="65"/>
+      <c r="K113" s="65"/>
+      <c r="L113" s="65"/>
+      <c r="M113" s="65"/>
+      <c r="N113" s="65"/>
+      <c r="O113" s="65"/>
+      <c r="P113" s="65"/>
+      <c r="Q113" s="65"/>
     </row>
     <row r="114" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D114" s="67"/>
-      <c r="E114" s="67"/>
-      <c r="F114" s="67"/>
-      <c r="G114" s="67"/>
-      <c r="H114" s="67"/>
-      <c r="I114" s="67"/>
-      <c r="J114" s="67"/>
-      <c r="K114" s="67"/>
-      <c r="L114" s="67"/>
-      <c r="M114" s="67"/>
-      <c r="N114" s="67"/>
-      <c r="O114" s="67"/>
-      <c r="P114" s="67"/>
-      <c r="Q114" s="67"/>
+      <c r="D114" s="65"/>
+      <c r="E114" s="65"/>
+      <c r="F114" s="65"/>
+      <c r="G114" s="65"/>
+      <c r="H114" s="65"/>
+      <c r="I114" s="65"/>
+      <c r="J114" s="65"/>
+      <c r="K114" s="65"/>
+      <c r="L114" s="65"/>
+      <c r="M114" s="65"/>
+      <c r="N114" s="65"/>
+      <c r="O114" s="65"/>
+      <c r="P114" s="65"/>
+      <c r="Q114" s="65"/>
     </row>
     <row r="115" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D115" s="67"/>
-      <c r="E115" s="67"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="67"/>
-      <c r="H115" s="67"/>
-      <c r="I115" s="67"/>
-      <c r="J115" s="67"/>
-      <c r="K115" s="67"/>
-      <c r="L115" s="67"/>
-      <c r="M115" s="67"/>
-      <c r="N115" s="67"/>
-      <c r="O115" s="67"/>
-      <c r="P115" s="67"/>
-      <c r="Q115" s="67"/>
+      <c r="D115" s="65"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="65"/>
+      <c r="H115" s="65"/>
+      <c r="I115" s="65"/>
+      <c r="J115" s="65"/>
+      <c r="K115" s="65"/>
+      <c r="L115" s="65"/>
+      <c r="M115" s="65"/>
+      <c r="N115" s="65"/>
+      <c r="O115" s="65"/>
+      <c r="P115" s="65"/>
+      <c r="Q115" s="65"/>
     </row>
     <row r="116" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D116" s="67"/>
-      <c r="E116" s="67"/>
-      <c r="F116" s="67"/>
-      <c r="G116" s="67"/>
-      <c r="H116" s="67"/>
-      <c r="I116" s="67"/>
-      <c r="J116" s="67"/>
-      <c r="K116" s="67"/>
-      <c r="L116" s="67"/>
-      <c r="M116" s="67"/>
-      <c r="N116" s="67"/>
-      <c r="O116" s="67"/>
-      <c r="P116" s="67"/>
-      <c r="Q116" s="67"/>
+      <c r="D116" s="65"/>
+      <c r="E116" s="65"/>
+      <c r="F116" s="65"/>
+      <c r="G116" s="65"/>
+      <c r="H116" s="65"/>
+      <c r="I116" s="65"/>
+      <c r="J116" s="65"/>
+      <c r="K116" s="65"/>
+      <c r="L116" s="65"/>
+      <c r="M116" s="65"/>
+      <c r="N116" s="65"/>
+      <c r="O116" s="65"/>
+      <c r="P116" s="65"/>
+      <c r="Q116" s="65"/>
     </row>
     <row r="117" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D117" s="67"/>
-      <c r="E117" s="67"/>
-      <c r="F117" s="67"/>
-      <c r="G117" s="67"/>
-      <c r="H117" s="67"/>
-      <c r="I117" s="67"/>
-      <c r="J117" s="67"/>
-      <c r="K117" s="67"/>
-      <c r="L117" s="67"/>
-      <c r="M117" s="67"/>
-      <c r="N117" s="67"/>
-      <c r="O117" s="67"/>
-      <c r="P117" s="67"/>
-      <c r="Q117" s="67"/>
+      <c r="D117" s="65"/>
+      <c r="E117" s="65"/>
+      <c r="F117" s="65"/>
+      <c r="G117" s="65"/>
+      <c r="H117" s="65"/>
+      <c r="I117" s="65"/>
+      <c r="J117" s="65"/>
+      <c r="K117" s="65"/>
+      <c r="L117" s="65"/>
+      <c r="M117" s="65"/>
+      <c r="N117" s="65"/>
+      <c r="O117" s="65"/>
+      <c r="P117" s="65"/>
+      <c r="Q117" s="65"/>
     </row>
     <row r="118" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D118" s="67"/>
-      <c r="E118" s="67"/>
-      <c r="F118" s="67"/>
-      <c r="G118" s="67"/>
-      <c r="H118" s="67"/>
-      <c r="I118" s="67"/>
-      <c r="J118" s="67"/>
-      <c r="K118" s="67"/>
-      <c r="L118" s="67"/>
-      <c r="M118" s="67"/>
-      <c r="N118" s="67"/>
-      <c r="O118" s="67"/>
-      <c r="P118" s="67"/>
-      <c r="Q118" s="67"/>
+      <c r="D118" s="65"/>
+      <c r="E118" s="65"/>
+      <c r="F118" s="65"/>
+      <c r="G118" s="65"/>
+      <c r="H118" s="65"/>
+      <c r="I118" s="65"/>
+      <c r="J118" s="65"/>
+      <c r="K118" s="65"/>
+      <c r="L118" s="65"/>
+      <c r="M118" s="65"/>
+      <c r="N118" s="65"/>
+      <c r="O118" s="65"/>
+      <c r="P118" s="65"/>
+      <c r="Q118" s="65"/>
     </row>
     <row r="119" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D119" s="67"/>
-      <c r="E119" s="67"/>
-      <c r="F119" s="67"/>
-      <c r="G119" s="67"/>
-      <c r="H119" s="67"/>
-      <c r="I119" s="67"/>
-      <c r="J119" s="67"/>
-      <c r="K119" s="67"/>
-      <c r="L119" s="67"/>
-      <c r="M119" s="67"/>
-      <c r="N119" s="67"/>
-      <c r="O119" s="67"/>
-      <c r="P119" s="67"/>
-      <c r="Q119" s="67"/>
+      <c r="D119" s="65"/>
+      <c r="E119" s="65"/>
+      <c r="F119" s="65"/>
+      <c r="G119" s="65"/>
+      <c r="H119" s="65"/>
+      <c r="I119" s="65"/>
+      <c r="J119" s="65"/>
+      <c r="K119" s="65"/>
+      <c r="L119" s="65"/>
+      <c r="M119" s="65"/>
+      <c r="N119" s="65"/>
+      <c r="O119" s="65"/>
+      <c r="P119" s="65"/>
+      <c r="Q119" s="65"/>
     </row>
     <row r="120" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D120" s="67"/>
-      <c r="E120" s="67"/>
-      <c r="F120" s="67"/>
-      <c r="G120" s="67"/>
-      <c r="H120" s="67"/>
-      <c r="I120" s="67"/>
-      <c r="J120" s="67"/>
-      <c r="K120" s="67"/>
-      <c r="L120" s="67"/>
-      <c r="M120" s="67"/>
-      <c r="N120" s="67"/>
-      <c r="O120" s="67"/>
-      <c r="P120" s="67"/>
-      <c r="Q120" s="67"/>
+      <c r="D120" s="65"/>
+      <c r="E120" s="65"/>
+      <c r="F120" s="65"/>
+      <c r="G120" s="65"/>
+      <c r="H120" s="65"/>
+      <c r="I120" s="65"/>
+      <c r="J120" s="65"/>
+      <c r="K120" s="65"/>
+      <c r="L120" s="65"/>
+      <c r="M120" s="65"/>
+      <c r="N120" s="65"/>
+      <c r="O120" s="65"/>
+      <c r="P120" s="65"/>
+      <c r="Q120" s="65"/>
     </row>
     <row r="121" spans="4:17" x14ac:dyDescent="0.4">
-      <c r="D121" s="67"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="67"/>
-      <c r="G121" s="67"/>
-      <c r="H121" s="67"/>
-      <c r="I121" s="67"/>
-      <c r="J121" s="67"/>
-      <c r="K121" s="67"/>
-      <c r="L121" s="67"/>
-      <c r="M121" s="67"/>
-      <c r="N121" s="67"/>
-      <c r="O121" s="67"/>
-      <c r="P121" s="67"/>
-      <c r="Q121" s="67"/>
+      <c r="D121" s="65"/>
+      <c r="E121" s="65"/>
+      <c r="F121" s="65"/>
+      <c r="G121" s="65"/>
+      <c r="H121" s="65"/>
+      <c r="I121" s="65"/>
+      <c r="J121" s="65"/>
+      <c r="K121" s="65"/>
+      <c r="L121" s="65"/>
+      <c r="M121" s="65"/>
+      <c r="N121" s="65"/>
+      <c r="O121" s="65"/>
+      <c r="P121" s="65"/>
+      <c r="Q121" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/storage/app/assessTemplate/renovation.xlsx
+++ b/storage/app/assessTemplate/renovation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\assessTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5AD080-10EF-4522-B43A-36EFCF992494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F763A1C-CABA-4140-BA6A-7A471CB77833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3AD99582-2449-4C94-B98B-43D8E1CCF0F2}"/>
+    <workbookView xWindow="45" yWindow="45" windowWidth="28755" windowHeight="15435" xr2:uid="{3AD99582-2449-4C94-B98B-43D8E1CCF0F2}"/>
   </bookViews>
   <sheets>
     <sheet name="改装物件の評価計算式" sheetId="2" r:id="rId1"/>
@@ -459,7 +459,7 @@
     <numFmt numFmtId="178" formatCode="0.0%"/>
     <numFmt numFmtId="179" formatCode="0.0000%"/>
     <numFmt numFmtId="180" formatCode="0.00000000_ "/>
-    <numFmt numFmtId="182" formatCode="General\%"/>
+    <numFmt numFmtId="181" formatCode="General\%"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1218,6 +1218,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1226,30 +1237,6 @@
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="6" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="11" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="32" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="35" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1281,15 +1268,28 @@
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="6" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="11" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="32" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="35" xfId="4" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1649,8 +1649,8 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
       <c r="R1" s="3" t="s">
         <v>49</v>
       </c>
@@ -1921,7 +1921,7 @@
       <c r="Q8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="85"/>
+      <c r="R8" s="67"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -1947,7 +1947,7 @@
       <c r="G9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="84"/>
+      <c r="H9" s="66"/>
       <c r="I9" s="2" t="s">
         <v>13</v>
       </c>
@@ -2001,7 +2001,7 @@
       <c r="Q10" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="86"/>
+      <c r="R10" s="68"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -2124,10 +2124,10 @@
       <c r="N13" s="25"/>
       <c r="O13" s="26"/>
       <c r="P13" s="2"/>
-      <c r="Q13" s="76" t="s">
+      <c r="Q13" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="R13" s="79"/>
+      <c r="R13" s="76"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -2158,8 +2158,8 @@
       <c r="N14" s="2"/>
       <c r="O14" s="31"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="80"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="77"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -2203,15 +2203,15 @@
       <c r="K15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="82" t="s">
+      <c r="L15" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
       <c r="O15" s="31"/>
       <c r="P15" s="2"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="81"/>
+      <c r="Q15" s="75"/>
+      <c r="R15" s="78"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -2237,7 +2237,7 @@
       <c r="G16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="84"/>
+      <c r="H16" s="66"/>
       <c r="I16" s="2" t="s">
         <v>13</v>
       </c>
@@ -2599,10 +2599,10 @@
       <c r="I25" s="2"/>
       <c r="J25" s="60"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="83" t="s">
+      <c r="L25" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="M25" s="83"/>
+      <c r="M25" s="80"/>
       <c r="N25" s="59"/>
       <c r="O25" s="20"/>
       <c r="P25" s="2"/>
@@ -2656,22 +2656,22 @@
     </row>
     <row r="27" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
-      <c r="B27" s="66" t="s">
+      <c r="B27" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="69"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="69"/>
-      <c r="O27" s="70"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="81"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -2689,20 +2689,20 @@
     </row>
     <row r="28" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="72"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="84"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -2720,20 +2720,20 @@
     </row>
     <row r="29" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="71"/>
-      <c r="O29" s="72"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="83"/>
+      <c r="L29" s="83"/>
+      <c r="M29" s="83"/>
+      <c r="N29" s="83"/>
+      <c r="O29" s="84"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -2751,20 +2751,20 @@
     </row>
     <row r="30" spans="1:31" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="74"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="86"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
@@ -4464,17 +4464,14 @@
       <c r="Q121" s="65"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="7">
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="C27:O30"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="Q13:Q15"/>
     <mergeCell ref="R13:R15"/>
     <mergeCell ref="L15:N15"/>
     <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="C27:O27"/>
-    <mergeCell ref="C28:O28"/>
-    <mergeCell ref="C29:O29"/>
-    <mergeCell ref="C30:O30"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
